--- a/extenbooks/S1703_extenbook.xlsx
+++ b/extenbooks/S1703_extenbook.xlsx
@@ -863,7 +863,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>**Status**: ingested</t>
+          <t>**Status**: book_period_validated</t>
         </is>
       </c>
     </row>
@@ -1826,11 +1826,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1853,76 +1853,6 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Personal Income Dist above $200k (Fig 17.3)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>chapter</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>extenbook_published</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>phases_completed</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>["3_research", "4_adequacy", "5_ingestion", "6_extension", "7_replication", "8_output"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>artifacts</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>{"research_json": "Technical/research/S1703_research.json", "adequacy_report": "Technical/docs/chapters/CH17_ADEQUACY_REPORT.json", "dpr": "Technical/docs/series/S1703_DPR.md", "epr": "Technical/docs/series/S1703_EPR.md", "loader": "Technical/code/L01_loaders/L01_S1703_load.py", "processor": "Technical/code/P02_processors/P02_S1703_construct.py", "validator": "Technical/code/V03_validators/V03_S1703_validate.py", "processed": "Technical/data/processed/S1703.parquet", "chopped_csv": "Technical/chopped/S1703.csv"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>updated_at</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-05-18T22:56:16.880881+00:00</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/extenbooks/S1703_extenbook.xlsx
+++ b/extenbooks/S1703_extenbook.xlsx
@@ -810,7 +810,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A117"/>
+  <dimension ref="A1:A116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -849,147 +849,147 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>**Phase**: 5 (Ingestion)</t>
+          <t>**Series ID**: S1703</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>**Series ID**: S1703</t>
+          <t>**Status**: book_period_validated</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>**Status**: book_period_validated</t>
+          <t>**Authored**: 2026-05-18</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>**Authored**: 2026-05-18</t>
-        </is>
-      </c>
+      <c r="A10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="A12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>## 1. Definition</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>## 1. Definition</t>
-        </is>
-      </c>
+      <c r="A14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Cross-sectional snapshot at Tax Year 2011: the cumulative probability from</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Cross-sectional snapshot at Tax Year 2011: the cumulative probability from</t>
+          <t>above (survival function) of personal income (AGI), restricted to bins with</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>above (survival function) of personal income (AGI), restricted to bins with</t>
+          <t>midpoint at or above $200,000 (the top ~3% of returns). Appears in Shaikh</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>midpoint at or above $200,000 (the top ~3% of returns). Appears in Shaikh</t>
+          <t>(2016) as **Figure 17.3** (p. 753), plotted on a log-log scale to test for</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>(2016) as **Figure 17.3** (p. 753), plotted on a log-log scale to test for</t>
+          <t>Pareto behaviour.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Pareto behaviour.</t>
-        </is>
-      </c>
+      <c r="A20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr"/>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>## 2. Why it matters in Chapter 17</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>## 2. Why it matters in Chapter 17</t>
-        </is>
-      </c>
+      <c r="A22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr"/>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>The top 3% of the IRS 2011 personal income distribution is approximately</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>The top 3% of the IRS 2011 personal income distribution is approximately</t>
+          <t>Pareto — appears as a straight line on a log-log plot. Pareto exponent</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Pareto — appears as a straight line on a log-log plot. Pareto exponent</t>
+          <t>estimated by OLS on log(survival) vs log(midpoint).</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>estimated by OLS on log(survival) vs log(midpoint).</t>
-        </is>
-      </c>
+      <c r="A26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr"/>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>## 3. Source</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>## 3. Source</t>
-        </is>
-      </c>
+      <c r="A28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr"/>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Same as S1702: IRS Statistics of Income (SOI) Publication 1304 Table 1.4,</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Same as S1702: IRS SOI Publication 1304 Table 1.4, Tax Year 2011 (via</t>
+          <t>Tax Year 2011 (from the published Chapter 17 appendix data tables; Shaikh</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>`Appendix17_USIRS2011.xlsx`).</t>
+          <t>2016, Appendix 17.2).</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1. **Column-fix** — use FPR017_C5 not FPR017_C3 (Phase 4).</t>
+          <t>1. **Column-fix** — use FPR017_C5 not FPR017_C3.</t>
         </is>
       </c>
     </row>
@@ -1090,14 +1090,14 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">   (NaN) and `Cumulative Frequency from Above = 0` for this bin; per</t>
+          <t xml:space="preserve">   (NaN) and `Cumulative Frequency from Above = 0` for this bin; we do not</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">   anti-synthetic rule we do not impute a midpoint. Phase 4 confirmed.</t>
+          <t xml:space="preserve">   impute a midpoint (no value invented).</t>
         </is>
       </c>
     </row>
@@ -1152,7 +1152,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>- CD legacy: S104; CD2 legacy: S104</t>
+          <t>- Earlier replications used the identifier S104</t>
         </is>
       </c>
     </row>
@@ -1193,14 +1193,14 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>noise). Achieved: MAE 0.0, max 0.0%, n=6. PASS. Phase 4 spot-checks match.</t>
+          <t>noise). Achieved: MAE 0.0, max 0.0%, n=6. PASS. Spot-checks match.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Pareto alpha estimated ~1.5-2.0; recorded in P02 run summary.</t>
+          <t>Pareto alpha estimated ~1.5-2.0.</t>
         </is>
       </c>
     </row>
@@ -1223,260 +1223,253 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>**Phase**: 6 (Extension)</t>
+          <t>**Construction**: `composite`</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>**Construction**: `composite`</t>
+          <t>**Content type**: `cross_sectional`</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>**Content type**: `cross_sectional`</t>
+          <t>**Extension method**: `not_applicable_cross_sectional`</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>**Extension method**: `not_applicable_cross_sectional`</t>
+          <t>**Status v1**: complete (no extension to perform)</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>**Status v1**: complete (no extension to perform)</t>
-        </is>
-      </c>
+      <c r="A78" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr"/>
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="A80" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr"/>
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>## 1. Why this series cannot be extended</t>
+        </is>
+      </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>## 1. Why this series cannot be extended</t>
-        </is>
-      </c>
+      <c r="A82" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr"/>
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>S1703 is a cross-sectional snapshot at a single tax year (2011). Under the</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>S1703 is a cross-sectional snapshot at a single tax year (2011). Per</t>
+          <t>rule that extensions apply only to time-series data, no extension is</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>anu-framework: "Extensions ONLY apply to time_series type." No extension is</t>
+          <t>performed.</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>performed.</t>
-        </is>
-      </c>
+      <c r="A86" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr"/>
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>A multi-year EPTC reconstruction (1996-2008 per Shaikh, Papanikolaou, Weiner</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A multi-year EPTC reconstruction (1996-2008 per Shaikh, Papanikolaou, Weiner</t>
+          <t>2014, cited at p. 753) would be a separate registry exercise — out of scope</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2014, cited at p. 753) would be a separate registry exercise — out of scope</t>
+          <t>for S1703.</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>for S1703.</t>
-        </is>
-      </c>
+      <c r="A90" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr"/>
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>## 2. Top-bin drop disclosure (no fabricated values)</t>
+        </is>
+      </c>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>## 2. Top-bin drop disclosure (anti-synthetic)</t>
-        </is>
-      </c>
+      <c r="A92" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr"/>
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>The open-ended `$10,000,000 or more` IRS bin has NO midpoint in the</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>The open-ended `$10,000,000 or more` IRS bin has NO midpoint in the</t>
+          <t>Appendix 17.2 spreadsheet and `Cumulative Frequency from Above = 0` for that</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Appendix 17.2 spreadsheet and `Cumulative Frequency from Above = 0` for that</t>
+          <t>bin. To avoid fabricating data, we do NOT impute a midpoint (e.g.,</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>bin. Per the No-Synthetic rule, we do NOT impute a midpoint (e.g.,</t>
+          <t>$15M or $50M) and we do NOT include the bin in the plotted survival points.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>$15M or $50M) and we do NOT include the bin in the plotted survival points.</t>
+          <t>This matches Shaikh's own Fig 17.3 which terminates at the $5M-$10M bin.</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>This matches Shaikh's own Fig 17.3 which terminates at the $5M-$10M bin.</t>
-        </is>
-      </c>
+      <c r="A98" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr"/>
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>## 3. Pareto exponent estimation</t>
+        </is>
+      </c>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>## 3. Pareto exponent estimation</t>
-        </is>
-      </c>
+      <c r="A100" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr"/>
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>OLS in log-log space:</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>OLS in log-log space:</t>
+          <t>`ln(P(Y &gt; y)) = a - alpha * ln(y)`</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>`ln(P(Y &gt; y)) = a - alpha * ln(y)`</t>
+          <t>estimated over the six top-tail bins ($350k through $7.5M midpoints).</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>estimated over the six top-tail bins ($350k through $7.5M midpoints).</t>
+          <t>Slight non-monotonicity at $3.5M / $7.5M reflects IRS sample noise; we do</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Slight non-monotonicity at $3.5M / $7.5M reflects IRS sample noise; we do</t>
+          <t>NOT smooth (the value is preserved verbatim from the workbook).</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>NOT smooth (the value is preserved verbatim from the workbook).</t>
-        </is>
-      </c>
+      <c r="A106" t="inlineStr"/>
     </row>
     <row r="107">
-      <c r="A107" t="inlineStr"/>
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>## 4. Source substitutions and forecast data</t>
+        </is>
+      </c>
     </row>
     <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>## 4. No-Proxy / No-Synthetic</t>
-        </is>
-      </c>
+      <c r="A108" t="inlineStr"/>
     </row>
     <row r="109">
-      <c r="A109" t="inlineStr"/>
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>The IRS data is itself the canonical authoritative source. Open-bin</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>The IRS data is itself the canonical authoritative source. Open-bin</t>
+          <t>midpoints come directly from Shaikh's Appendix 17.2 spreadsheet — preserved</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>midpoints come directly from Shaikh's Appendix 17.2 spreadsheet — preserved</t>
+          <t>verbatim, never re-derived. The $10M+ bin is excluded (no fabrication).</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>verbatim, never re-derived. The $10M+ bin is excluded (no fabrication).</t>
-        </is>
-      </c>
+      <c r="A112" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" t="inlineStr"/>
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>## 5. Divergence from earlier replications</t>
+        </is>
+      </c>
     </row>
     <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>## 5. CD2 divergence pre-disclosure</t>
-        </is>
-      </c>
+      <c r="A114" t="inlineStr"/>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr"/>
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>An earlier replication's S104 reference values were the Frequency column</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>CD2's S104 reference_values were the Frequency column (FPR017_C3) — Phase 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>corrected to column F (FPR017_C5).</t>
+          <t>(FPR017_C3), corrected here to column F (FPR017_C5).</t>
         </is>
       </c>
     </row>
@@ -1811,7 +1804,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-05-18T23:12:20.695267+00:00</t>
+          <t>2026-07-02T06:20:43.809586+00:00</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S1703_extenbook.xlsx
+++ b/extenbooks/S1703_extenbook.xlsx
@@ -1804,7 +1804,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-07-02T06:20:43.809586+00:00</t>
+          <t>2026-07-11T03:44:23.952630+00:00</t>
         </is>
       </c>
     </row>
@@ -1819,11 +1819,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1846,6 +1846,162 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>primary_source</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>IRS_SOI_2011_PUB1304_TABLE_1_4</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>composite</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>book_period_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>validation_class</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>book_verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>triage</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>{"verdict": "publish", "reason": "KB-verified: figure 17.3 caption and in-text passage (pp.752\u2013753) match; IRS SOI Publication 1304 Table 1.4 (2011) sourcing confirmed; Pareto exponent by OLS on log-log; $10M+ open bin dropped. Verbatim quotes match.", "date": "2026-06-11"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>dpr</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S1703_DPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>epr</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S1703_EPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Fig 17.3; Pareto exponent estimated by OLS on log-log; $10M+ bin dropped.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>content_type</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>cross_sectional</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>cumulative_probability_from_above_dimensionless</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>proxy</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>chapter</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
